--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_14-04-2026.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
